--- a/tests/fixtures/calcchain/calcchain-regression.xlsx
+++ b/tests/fixtures/calcchain/calcchain-regression.xlsx
@@ -98,11 +98,14 @@
         <v>3</v>
       </c>
       <c r="F3">
-        <f>D3*2</f>
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="G3">
         <v>4</v>
+      </c>
+      <c r="M3">
+        <f>D3*2</f>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
